--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>20/07 19:45</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>28/07 19:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>20/07 19:45</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>21/07 00:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>50</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>22/07 00:15</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>50</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>22/07 18:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>20/07 09:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>25/07 16:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>45</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>27/07 17:15</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>50</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>21/07 18:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>27/07 17:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>50</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>20/07 14:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F14" t="n">
+        <v>2.75</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>22/07 00:15</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>60</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>20/07 09:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F16" t="n">
+        <v>1.9</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>20/07 19:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F17" t="n">
+        <v>2.2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>20/07 20:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F18" t="n">
+        <v>2.9</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>26/07 18:30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>40</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>20/07 12:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="F20" t="n">
+        <v>5.75</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>26/07 23:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>40</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>24/07 18:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>20/07 20:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>40</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>20/07 20:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F24" t="n">
+        <v>2.75</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>27/07 00:15</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>40</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>40</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,142 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45858.08723607584</v>
+        <v>45858.08723607639</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Basketball | H 1 (−19.5)P | Minnesota </t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Minnesota Lynx – Chicago SkyÉtats-Unis - WNBA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>H 1 (−19.5)P</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>23/07 00:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>36,5%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+14,9%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45858.17118759674</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Monterrey </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Monterrey – Atlas FCLiga MX</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>27/07 01:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45858.17118759674</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | Palmeiras </t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Palmeiras – Atletico MineiroBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>20/07 20:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>25,6%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+8,78%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45858.17118759674</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>23/07 00:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
+      <c r="F27" t="n">
+        <v>3.15</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45858.17118759674</v>
+        <v>45858.17118759259</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>27/07 01:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>45</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45858.17118759674</v>
+        <v>45858.17118759259</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>20/07 20:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
+      <c r="F29" t="n">
+        <v>4.25</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,97 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45858.17118759674</v>
+        <v>45858.17118759259</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Barracas C</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Barracas Central – Independiente RivadaviaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>20/07 17:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+2,78%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45858.2277255648</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Levski Sof</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Levski Sofia – Sporting BragaLigue Europa</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>24/07 17:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+1,28%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45858.2277255648</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>20/07 17:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>40</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45858.2277255648</v>
+        <v>45858.22772556713</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>24/07 17:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>45</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,97 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45858.2277255648</v>
+        <v>45858.22772556713</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | H 2 (−1.5) | Matej Dodi</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Matej Dodig – Francesco PassaroATP - Umag</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>H 2 (−1.5)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>20/07 19:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>61,0%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+14,6%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45858.27273223961</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Basketball | Moins que 39.52e période | Chine (F) </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Chine (F) – Corée du S (F)International - Cpe d'Asie (F)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Moins que 39.52e période</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>20/07 08:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>50,9%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+4,33%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45858.27273223961</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>20/07 19:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
+      <c r="F32" t="n">
+        <v>1.88</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45858.27273223961</v>
+        <v>45858.27273224537</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>20/07 08:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="F33" t="n">
+        <v>2.05</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,52 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45858.27273223961</v>
+        <v>45858.27273224537</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Universita</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova – FC Universitatea ClujLiga 1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>28/07 18:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+2,22%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45858.30633615959</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>28/07 18:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>35</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,97 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45858.30633615959</v>
+        <v>45858.30633615741</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 6.5 - tir cadré2e équipe | Sport Reci</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sport Recife – BotafogoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>20/07 20:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>24,5%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+4,20%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45858.35321477596</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 10.5 - tirs2e équipe | Flamengo –</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Flamengo – FluminenseBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>20/07 22:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>36,8%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+1,16%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45858.35321477596</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>20/07 20:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
+      <c r="F35" t="n">
+        <v>4.25</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45858.35321477596</v>
+        <v>45858.35321478009</v>
       </c>
     </row>
     <row r="36">
@@ -1969,10 +1967,8 @@
           <t>20/07 22:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F36" t="n">
+        <v>2.75</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1985,7 +1981,142 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45858.35321477596</v>
+        <v>45858.35321478009</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 6.5 - tir cadré1re équipe | Internacio</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Internacional RS – Ceara CEBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>20/07 14:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>31,4%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+25,6%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45858.3909981397</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Albirex Ni</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Albirex Niigata – Sanfrecce HiroshimaJ-League</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>20/07 10:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+4,78%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45858.3909981397</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | X - aces | Jil Teichm</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Jil Teichmann – Irina-Camelia BeguWTA - Iasi</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>20/07 14:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>25,8%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+3,32%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45858.3909981397</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>20/07 14:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>4</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45858.3909981397</v>
+        <v>45858.39099813657</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>20/07 10:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>45</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45858.3909981397</v>
+        <v>45858.39099813657</v>
       </c>
     </row>
     <row r="39">
@@ -2100,10 +2096,8 @@
           <t>20/07 14:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>4</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2116,7 +2110,277 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45858.3909981397</v>
+        <v>45858.39099813657</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 6.5 - tir cadré | Internacio</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Internacional RS – Ceara CEBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Moins que 6.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>20/07 14:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>31,9%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+14,7%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45858.43374476369</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Beach volley | Moins que 37.51er set | B.Ruysscha</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Beach volley</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B.Ruysschaert / I.van Den Broeck – A.Parkkinen / V.PrihtiFuture - Leuven - QF</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Moins que 37.51er set</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>20/07 10:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>44,1%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+5,84%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45858.43374476369</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 6.5 - tir cadré | Flamengo –</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Flamengo – FluminenseBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Moins que 6.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>20/07 22:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>31,4%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+3,76%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45858.43374476369</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Basketball | Moins que 37.51re période | Japon (F) </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Japon (F) – Australie (F)International - Cpe d'Asie (F)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Moins que 37.51re période</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>20/07 11:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>47,8%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+2,79%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45858.43374476369</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 10.5 - tir cadré | Palmeiras </t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Palmeiras – Atletico MineiroBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>20/07 20:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>26,3%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+2,70%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45858.43374476369</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | Copenhague</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Copenhague – KF DritaEurope. Ligue des Champions (Q)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>22/07 17:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>24.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+2,25%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45858.43374476369</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>20/07 14:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F40" t="n">
+        <v>3.6</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45858.43374476369</v>
+        <v>45858.43374476852</v>
       </c>
     </row>
     <row r="41">
@@ -2184,10 +2182,8 @@
           <t>20/07 10:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F41" t="n">
+        <v>2.4</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2200,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45858.43374476369</v>
+        <v>45858.43374476852</v>
       </c>
     </row>
     <row r="42">
@@ -2229,10 +2225,8 @@
           <t>20/07 22:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F42" t="n">
+        <v>3.3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2245,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45858.43374476369</v>
+        <v>45858.43374476852</v>
       </c>
     </row>
     <row r="43">
@@ -2274,10 +2268,8 @@
           <t>20/07 11:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F43" t="n">
+        <v>2.15</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2290,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45858.43374476369</v>
+        <v>45858.43374476852</v>
       </c>
     </row>
     <row r="44">
@@ -2319,10 +2311,8 @@
           <t>20/07 20:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="F44" t="n">
+        <v>3.9</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2335,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45858.43374476369</v>
+        <v>45858.43374476852</v>
       </c>
     </row>
     <row r="45">
@@ -2364,10 +2354,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>24.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>24</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2380,7 +2368,142 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45858.43374476369</v>
+        <v>45858.43374476852</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 11.5 - tirs2e équipe | Gornik Zab</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Gornik Zabrze – Lechia GdanskPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Moins que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>20/07 12:45</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>54,0%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+25,3%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45858.47164310217</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 13.5 - tirs1re équipe | Motor Lubl</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Motor Lublin – Arka GdyniaPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Moins que 13.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>20/07 15:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52,5%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+19,7%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45858.47164310217</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 13.5 - tirs2e équipe | RKS Radomi</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>RKS Radomiak – Pogon SzczecinPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Moins que 13.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>20/07 18:15</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52,8%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+3,43%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45858.47164310217</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>20/07 12:45</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
+      <c r="F46" t="n">
+        <v>2.32</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45858.47164310217</v>
+        <v>45858.47164310185</v>
       </c>
     </row>
     <row r="47">
@@ -2442,10 +2440,8 @@
           <t>20/07 15:30</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
+      <c r="F47" t="n">
+        <v>2.28</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2458,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45858.47164310217</v>
+        <v>45858.47164310185</v>
       </c>
     </row>
     <row r="48">
@@ -2487,10 +2483,8 @@
           <t>20/07 18:15</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
+      <c r="F48" t="n">
+        <v>1.96</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2503,7 +2497,52 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45858.47164310217</v>
+        <v>45858.47164310185</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | Motor Lubl</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Motor Lublin – Arka GdyniaPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>20/07 15:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>44,2%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+6,02%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45858.53056797005</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>20/07 15:30</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F49" t="n">
+        <v>2.4</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,97 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45858.53056797005</v>
+        <v>45858.53056797454</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | GAIS – Hal</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>GAIS – Halmstads BKAllsvenskan</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>26/07 13:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+11,7%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45858.56460499315</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | Vitoria BA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Vitoria BA – BragantinoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>20/07 19:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>34,2%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+1,02%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45858.56460499315</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>26/07 13:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>50</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45858.56460499315</v>
+        <v>45858.56460498842</v>
       </c>
     </row>
     <row r="51">
@@ -2614,10 +2612,8 @@
           <t>20/07 19:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F51" t="n">
+        <v>2.95</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2630,7 +2626,142 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45858.56460499315</v>
+        <v>45858.56460498842</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Dunajska S</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Dunajska Streda – MFK Zemplin MichalovceFortuna Liga</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>26/07 16:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+2,17%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45858.59751474069</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Volleyball | 21-2 | Pays-Bas –</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Pays-Bas – ItalieInternational - Ligue des nations H.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>20/07 14:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>93,6%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+1,12%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45858.59751474069</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Gremio – A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Gremio – Alianza LimaCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>24/07 00:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+1,01%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45858.59751474069</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>26/07 16:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>40</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45858.59751474069</v>
+        <v>45858.59751474537</v>
       </c>
     </row>
     <row r="53">
@@ -2700,10 +2698,8 @@
           <t>20/07 14:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
+      <c r="F53" t="n">
+        <v>1.08</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2716,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45858.59751474069</v>
+        <v>45858.59751474537</v>
       </c>
     </row>
     <row r="54">
@@ -2745,10 +2741,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>40</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2761,7 +2755,97 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45858.59751474069</v>
+        <v>45858.59751474537</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Raphael Co</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Raphael Collignon – Vit KoprivaATP - Umag</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>20/07 15:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>61,2%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+10,1%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45858.64075670768</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football | 1X | Aris Limas</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Aris Limassol – Puskas AcademyCoupes d'Europe - Europa Conference</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>24/07 16:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>79,2%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+0,53%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45858.64075670768</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>20/07 15:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="F55" t="n">
+        <v>1.8</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45858.64075670768</v>
+        <v>45858.64075671296</v>
       </c>
     </row>
     <row r="56">
@@ -2829,10 +2827,8 @@
           <t>24/07 16:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
+      <c r="F56" t="n">
+        <v>1.27</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2845,7 +2841,97 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45858.64075670768</v>
+        <v>45858.64075671296</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Football | 2 1er but2e période | HB Torshav</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HB Torshavn – Brondby IFInternational - Clubs - Ligue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2 1er but2e période</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>24/07 18:45</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>64,6%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+0,20%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45858.68561257476</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football | 1X2e période | Omonia Nic</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Omonia Nicosie – Torp.KutaisiCoupes d'Europe - Europa Conference</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1X2e période</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>24/07 17:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>91,8%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+0,11%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45858.68561257476</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>24/07 18:45</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="F57" t="n">
+        <v>1.55</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45858.68561257476</v>
+        <v>45858.68561256945</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>24/07 17:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
+      <c r="F58" t="n">
+        <v>1.09</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,97 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45858.68561257476</v>
+        <v>45858.68561256945</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 13.5 - tirs1re équipe | Flamengo –</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Flamengo – FluminenseBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Moins que 13.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>20/07 22:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>36,4%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+7,23%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45858.72201676914</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Plus que 5.51er set2e participant | Francisco </t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Francisco Comesana – Tristan BoyerATP 250 Kitzbühel</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 5.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>21/07 09:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>39,0%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+5,17%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45858.72201676914</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>20/07 22:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F59" t="n">
+        <v>2.95</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45858.72201676914</v>
+        <v>45858.72201677084</v>
       </c>
     </row>
     <row r="60">
@@ -3001,10 +2999,8 @@
           <t>21/07 09:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F60" t="n">
+        <v>2.7</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3017,7 +3013,232 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45858.72201676914</v>
+        <v>45858.72201677084</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Bohemians </t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Bohemians 1905 – Slavia PragueSynot League</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>26/07 18:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2,50%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+50,2%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45858.7717199632</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Sparta Prague – FK Mlada BoleslavSynot League</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>27/07 18:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2,50%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+12,5%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45858.7717199632</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Sport Reci</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Sport Recife – BotafogoSérie A</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>20/07 20:30</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+8,34%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45858.7717199632</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 1.5 - tir cadré2e équipe | Cruzeiro –</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Cruzeiro – Juventude RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Moins que 1.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>20/07 19:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>25,2%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+0,83%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45858.7717199632</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set2e participant | Venus Will</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Venus Williams – Peyton StearnsWTA 500 Washington</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>21/07 14:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>6.90</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+0,29%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45858.7717199632</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>26/07 18:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>60</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45858.7717199632</v>
+        <v>45858.77171996528</v>
       </c>
     </row>
     <row r="62">
@@ -3087,10 +3085,8 @@
           <t>27/07 18:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>45</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3103,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45858.7717199632</v>
+        <v>45858.77171996528</v>
       </c>
     </row>
     <row r="63">
@@ -3132,10 +3128,8 @@
           <t>20/07 20:30</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>50</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3148,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45858.7717199632</v>
+        <v>45858.77171996528</v>
       </c>
     </row>
     <row r="64">
@@ -3177,10 +3171,8 @@
           <t>20/07 19:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3193,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45858.7717199632</v>
+        <v>45858.77171996528</v>
       </c>
     </row>
     <row r="65">
@@ -3222,10 +3214,8 @@
           <t>21/07 14:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>6.90</t>
-        </is>
+      <c r="F65" t="n">
+        <v>6.9</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3238,7 +3228,52 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45858.7717199632</v>
+        <v>45858.77171996528</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 28.5 - tirs | Flamengo –</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Flamengo – FluminenseBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 28.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>20/07 22:30</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>33,4%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+0,14%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45858.8043563379</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3257,10 +3257,8 @@
           <t>20/07 22:30</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>3</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3273,7 +3271,187 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45858.8043563379</v>
+        <v>45858.80435634259</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CS 2 de Ma</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CS 2 de Mayo – Club Sportivo LuquenoPrimera Division</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>25/07 21:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+33,9%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45858.85083906189</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Union Sant</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Union Santa Fe – CA TigreLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>26/07 00:15</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+11,0%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45858.85083906189</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Moins que 4.51er set1er participant | Jesper De </t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Jesper De Jong – Mili Poljicak385076e7 ATP 250 Umag</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Moins que 4.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>22/07 14:30</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>27,2%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+0,69%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45858.85083906189</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Tie-break: Oui | Alexander </t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Alexander Shevchenko – Daniel Elahi GalanATP 250 Kitzbühel</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Tie-break: Oui</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>21/07 09:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>40,9%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+0,20%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45858.85083906189</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,10 +3300,8 @@
           <t>25/07 21:30</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>45</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3316,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45858.85083906189</v>
+        <v>45858.8508390625</v>
       </c>
     </row>
     <row r="68">
@@ -3345,10 +3343,8 @@
           <t>26/07 00:15</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>45</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3361,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45858.85083906189</v>
+        <v>45858.8508390625</v>
       </c>
     </row>
     <row r="69">
@@ -3390,10 +3386,8 @@
           <t>22/07 14:30</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F69" t="n">
+        <v>3.7</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3406,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45858.85083906189</v>
+        <v>45858.8508390625</v>
       </c>
     </row>
     <row r="70">
@@ -3435,10 +3429,8 @@
           <t>21/07 09:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="F70" t="n">
+        <v>2.45</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3451,7 +3443,142 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45858.85083906189</v>
+        <v>45858.8508390625</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FC Hradec </t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>FC Hradec Kralove – MFK KarvinaSynot League</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>26/07 15:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+7,48%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45858.8897619559</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Vitoria BA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Vitoria BA – Sport RecifeSérie A</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>24/07 00:30</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+4,85%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45858.8897619559</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 4.51er set2e participant | Venus Will</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Venus Williams – Peyton StearnsWTA 500 Washington</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Moins que 4.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>21/07 14:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>13,4%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+4,00%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45858.8897619559</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3472,10 +3472,8 @@
           <t>26/07 15:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F71" t="n">
+        <v>40</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3488,7 +3486,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45858.8897619559</v>
+        <v>45858.88976195602</v>
       </c>
     </row>
     <row r="72">
@@ -3517,10 +3515,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>45</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3533,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45858.8897619559</v>
+        <v>45858.88976195602</v>
       </c>
     </row>
     <row r="73">
@@ -3562,10 +3558,8 @@
           <t>21/07 14:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>7.75</t>
-        </is>
+      <c r="F73" t="n">
+        <v>7.75</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3578,7 +3572,187 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45858.8897619559</v>
+        <v>45858.88976195602</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Independie</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia – CA BelgranoLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>26/07 00:15</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+34,9%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45858.93197495464</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CD Recolet</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CD Recoleta – Cerro PortenoPrimera Division</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>26/07 21:30</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+26,7%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45858.93197495464</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | SK Sigma O</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SK Sigma Olomouc – FK Dukla PragueSynot League</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>26/07 15:00</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+7,18%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45858.93197495464</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Sportivo A</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sportivo Ameliano – Club OlimpiaPrimera Division</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>27/07 18:30</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>35.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+1,69%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45858.93197495464</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-20.xlsx
+++ b/data/valuebets_database_2025-07-20.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3601,10 +3601,8 @@
           <t>26/07 00:15</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F74" t="n">
+        <v>60</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3617,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45858.93197495464</v>
+        <v>45858.9319749537</v>
       </c>
     </row>
     <row r="75">
@@ -3646,10 +3644,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>45</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3662,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45858.93197495464</v>
+        <v>45858.9319749537</v>
       </c>
     </row>
     <row r="76">
@@ -3691,10 +3687,8 @@
           <t>26/07 15:00</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>40</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3707,7 +3701,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45858.93197495464</v>
+        <v>45858.9319749537</v>
       </c>
     </row>
     <row r="77">
@@ -3736,10 +3730,8 @@
           <t>27/07 18:30</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F77" t="n">
+        <v>35</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3752,7 +3744,52 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45858.93197495464</v>
+        <v>45858.9319749537</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Water-polo | 1 | France (F)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Water-polo</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>France (F) – Grande-Bretagne (F)Monde - Mondial (F)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>21/07 01:00</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>30,6%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+4,18%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45858.9744210257</v>
       </c>
     </row>
   </sheetData>
